--- a/stories/arbres/TREE-AUT-039.xlsx
+++ b/stories/arbres/TREE-AUT-039.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Tom est avec papa, sur le chemin de l'école. Tom a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom écoute papa. Tom entend les mots : ranger, caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-039.xlsx
+++ b/stories/arbres/TREE-AUT-039.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Tom est avec papa, sur le chemin de l'école. Tom a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom écoute papa. Tom entend les mots : ranger, caisse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Tom rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Tom rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Tom rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Tom rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Tom rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Tom a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Tom rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Tom a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Tom rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Tom a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Tom rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Tom rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Tom rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Tom rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Tom rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Tom rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Tom rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Tom rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-039.xlsx
+++ b/stories/arbres/TREE-AUT-039.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ranger après le jeu — sur le chemin de l'école</t>
+          <t>La caisse d'osier de Nino</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino marche vers l'école. Le banc de pierre est mouillé. Une feuille colle au bonnet. Il joue un peu, puis met les jouets dans la caisse d'osier.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Tom est avec papa, sur le chemin de l'école. Tom a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom écoute papa. Tom entend les mots : ranger, caisse.</t>
+          <t>Le réverbère est encore allumé. Une goutte tombe du toit, toute ronde. Elle éclate sur le banc de pierre. Le banc est froid, un peu vert de mousse. Un bonnet de laine attend sur le banc. Une feuille jaune y colle, toute plate. Le cartable de Nino est posé à côté. La fermeture fait un petit zzz. Papa tient une caisse d'osier par la corde. L'osier sent le foin sec. Maman boutonne son manteau, près de la grille. La grille de cave est froide et noire. Tu as mis ton bonnet, Nino ? Oui, maman. Il y a une feuille dessus. On la laisse. Elle est jolie. En ce moment, Nino touche la caisse. Les jouets dorment dedans, tout calmes. Je veux jouer un peu ! D'accord. Un petit moment. Après le jeu, on met dans la caisse. Ranger, c'est mettre dans la caisse. Dans la caisse. Puis on reprend le chemin de l'école.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,34 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Tom est avec papa, sur le chemin de l'école. Tom a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom écoute papa. Tom entend les mots : ranger, caisse.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le réverbère est encore allumé.
+narrateur|Une goutte tombe du toit, toute ronde.
+narrateur|Elle éclate sur le banc de pierre.
+narrateur|Le banc est froid, un peu vert de mousse.
+narrateur|Un bonnet de laine attend sur le banc.
+narrateur|Une feuille jaune y colle, toute plate.
+narrateur|Le cartable de Nino est posé à côté.
+narrateur|La fermeture fait un petit zzz.
+narrateur|Papa tient une caisse d'osier par la corde.
+narrateur|L'osier sent le foin sec.
+narrateur|Maman boutonne son manteau, près de la grille.
+narrateur|La grille de cave est froide et noire.
+maman|Tu as mis ton bonnet, Nino ?
+enfant-m|Oui, maman.
+enfant-m|Il y a une feuille dessus.
+papa|On la laisse.
+papa|Elle est jolie.
+narrateur|En ce moment, Nino touche la caisse.
+narrateur|Les jouets dorment dedans, tout calmes.
+enfant-m|Je veux jouer un peu !
+papa|D'accord.
+papa|Un petit moment.
+maman|Après le jeu, on met dans la caisse.
+papa|Ranger, c'est mettre dans la caisse.
+enfant-m|Dans la caisse.
+maman|Puis on reprend le chemin de l'école.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1389,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Nino joue où, un moment ? La cuisine, le jardin, ou la chambre ? La cuisine. Le jardin. Ou la chambre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,10 +1553,13 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>papa|Nino joue où, un moment ?
+maman|La cuisine, le jardin, ou la chambre ?
+narrateur|La cuisine.
+narrateur|Le jardin.
+narrateur|Ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1545,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Nino va vers la cuisine. Les carreaux sont froids sous les chaussettes. Ça sent l'orange pelée, tout près. Un zeste orange brille dans l'évier. La casserole fait un tout petit tic. Tu joues ici un moment. La caisse d'osier est près de la porte. Je joue, papa. Oui. Puis on range. On met dans la caisse. Nino pose un doigt sur le zeste. Il est un peu humide, un peu parfumé. Après le jeu, on range. Je suis avec toi. Une buée fine reste sur la vitre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1724,24 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On dit merci.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino va vers la cuisine.
+narrateur|Les carreaux sont froids sous les chaussettes.
+narrateur|Ça sent l'orange pelée, tout près.
+narrateur|Un zeste orange brille dans l'évier.
+narrateur|La casserole fait un tout petit tic.
+maman|Tu joues ici un moment.
+papa|La caisse d'osier est près de la porte.
+enfant-m|Je joue, papa.
+papa|Oui.
+papa|Puis on range.
+maman|On met dans la caisse.
+narrateur|Nino pose un doigt sur le zeste.
+narrateur|Il est un peu humide, un peu parfumé.
+papa|Après le jeu, on range.
+maman|Je suis avec toi.
+narrateur|Une buée fine reste sur la vitre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Ranger après le jeu.</t>
+          <t>Le zeste brille encore. Après le jeu, on met où ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,10 +1926,10 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le zeste brille encore.
+maman|Après le jeu, on met où ?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1902,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
+          <t>Oui. On range. On met dans la caisse. Ranger, c'est mettre dans la caisse. Dans la caisse. Bravo, Nino. Tu as fait du bon travail. Nino hoche la tête. La corde de l'osier t'attend. La casserole tic encore, tout petit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,10 +2098,18 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Oui.
+papa|On range.
+papa|On met dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino hoche la tête.
+maman|La corde de l'osier t'attend.
+narrateur|La casserole tic encore, tout petit.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2074,7 +2134,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu prends quel jeu ? Les cubes. Le livre. Ou la dînette.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,10 +2298,12 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+          <t>papa|Tu prends quel jeu ?
+narrateur|Les cubes.
+narrateur|Le livre.
+narrateur|Ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2266,7 +2328,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
+          <t>Nino a choisi les cubes. Ils sont en bois, un peu lourds. Clic, sur la table de la cuisine. Un cube jaune roule près du zeste. Tu poses une tour. Elle est haute. Elle est belle, Nino. La casserole tic encore. Après le jeu, on range. On met les cubes dans la caisse. Nino touche un cube lisse. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2468,21 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nino a choisi les cubes.
+narrateur|Ils sont en bois, un peu lourds.
+narrateur|Clic, sur la table de la cuisine.
+narrateur|Un cube jaune roule près du zeste.
+papa|Tu poses une tour.
+enfant-m|Elle est haute.
+maman|Elle est belle, Nino.
+narrateur|La casserole tic encore.
+papa|Après le jeu, on range.
+maman|On met les cubes dans la caisse.
+narrateur|Nino touche un cube lisse.
+papa|Bravo.
+papa|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2507,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,10 +2671,12 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2626,7 +2701,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. Les cubes ne cliquent plus. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Une miette d'orange reste sur le cube jaune.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,10 +2841,26 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|Les cubes ne cliquent plus.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Une miette d'orange reste sur le cube jaune.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2794,7 +2885,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec les cubes. C'était le matin. Après le jeu, il a mis dans la caisse. Une miette d'orange reste sur le cube jaune. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,10 +3025,18 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Une miette d'orange reste sur le cube jaune.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2962,7 +3061,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. Les cubes ne cliquent plus. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. Les cubes sont tièdes, encore.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,10 +3201,26 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|Les cubes ne cliquent plus.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|Les cubes sont tièdes, encore.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3130,7 +3245,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec les cubes. C'était après la sieste. Après le jeu, il a mis dans la caisse. Les cubes sont tièdes, encore. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,10 +3385,18 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Les cubes sont tièdes, encore.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3298,7 +3421,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. Les cubes ne cliquent plus. On range pour demain matin. C'est le soir. On range pour demain. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. Un cube bleu dort dans l'ombre de la table.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,10 +3561,26 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|Les cubes ne cliquent plus.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|Un cube bleu dort dans l'ombre de la table.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3466,7 +3605,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec les cubes. C'était le soir. Après le jeu, il a mis dans la caisse. Un cube bleu dort dans l'ombre de la table. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,10 +3745,18 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Un cube bleu dort dans l'ombre de la table.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3634,7 +3781,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Nino a choisi le livre. La couverture est lisse, un peu froide. Les pages sentent le papier. Tu tournes tout doux. Il y a un bateau. Oui. Un bateau rouge. Une miette d'orange reste au bord. Après le jeu, on range. On met le livre dans la caisse. Nino ferme le livre. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,10 +3921,21 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nino a choisi le livre.
+narrateur|La couverture est lisse, un peu froide.
+narrateur|Les pages sentent le papier.
+maman|Tu tournes tout doux.
+enfant-m|Il y a un bateau.
+papa|Oui.
+papa|Un bateau rouge.
+narrateur|Une miette d'orange reste au bord.
+maman|Après le jeu, on range.
+papa|On met le livre dans la caisse.
+narrateur|Nino ferme le livre.
+maman|Bravo.
+maman|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3802,7 +3960,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3966,10 +4124,12 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3994,7 +4154,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. Le livre est fermé. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Le bateau rouge reste sur la page.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4134,10 +4294,26 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|Le livre est fermé.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Le bateau rouge reste sur la page.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4162,7 +4338,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec le livre. C'était le matin. Après le jeu, il a mis dans la caisse. Le bateau rouge reste sur la page. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4302,10 +4478,18 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le bateau rouge reste sur la page.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4330,7 +4514,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. Le livre est fermé. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. Nino bâille, tout doux, près du livre.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4470,10 +4654,26 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|Le livre est fermé.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|Nino bâille, tout doux, près du livre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4498,7 +4698,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec le livre. C'était après la sieste. Après le jeu, il a mis dans la caisse. Nino bâille, tout doux, près du livre. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4638,10 +4838,18 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Nino bâille, tout doux, près du livre.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4666,7 +4874,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. Le livre est fermé. On range pour demain matin. C'est le soir. On range pour demain. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. La page sent encore le papier.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4806,10 +5014,26 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|Le livre est fermé.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|La page sent encore le papier.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4834,7 +5058,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec le livre. C'était le soir. Après le jeu, il a mis dans la caisse. La page sent encore le papier. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4974,10 +5198,18 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|La page sent encore le papier.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5002,7 +5234,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>Nino a choisi la dînette. Une tasse tape l'assiette. Toc. Ça sent encore l'orange, tout près. Tu sers le goûter ? Oui. C'est de l'orange. D'accord. Puis on range. La petite cuillère brille. Après le jeu, on met dans la caisse. La dînette va dans la caisse. Nino pose la tasse. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5142,10 +5374,23 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Nino a choisi la dînette.
+narrateur|Une tasse tape l'assiette.
+narrateur|Toc.
+narrateur|Ça sent encore l'orange, tout près.
+maman|Tu sers le goûter ?
+enfant-m|Oui.
+enfant-m|C'est de l'orange.
+papa|D'accord.
+papa|Puis on range.
+narrateur|La petite cuillère brille.
+maman|Après le jeu, on met dans la caisse.
+papa|La dînette va dans la caisse.
+narrateur|Nino pose la tasse.
+maman|Bravo.
+maman|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5170,7 +5415,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5334,10 +5579,12 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5362,7 +5609,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. La tasse ne tape plus. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Le pain n'est plus sur l'assiette.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5502,10 +5749,26 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|La tasse ne tape plus.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Le pain n'est plus sur l'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5530,7 +5793,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec la dînette. C'était le matin. Après le jeu, il a mis dans la caisse. Le pain n'est plus sur l'assiette. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5670,10 +5933,18 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le pain n'est plus sur l'assiette.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5698,7 +5969,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. La tasse ne tape plus. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. Les carreaux sont plus frais.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5838,10 +6109,26 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|La tasse ne tape plus.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|Les carreaux sont plus frais.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5866,7 +6153,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec la dînette. C'était après la sieste. Après le jeu, il a mis dans la caisse. Les carreaux sont plus frais. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6006,10 +6293,18 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Les carreaux sont plus frais.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6034,7 +6329,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la cuisine. La tasse ne tape plus. On range pour demain matin. C'est le soir. On range pour demain. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. La cuisine s'assombrit, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6174,10 +6469,26 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la cuisine.
+narrateur|La tasse ne tape plus.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|La cuisine s'assombrit, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6202,7 +6513,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la cuisine. Il a joué avec la dînette. C'était le soir. Après le jeu, il a mis dans la caisse. La cuisine s'assombrit, tout doux. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6342,10 +6653,18 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|La cuisine s'assombrit, tout doux.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6370,7 +6689,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Nino va vers le jardin. L'herbe est mouillée, toute brillante. Ça sent la terre fraîche. Un arrosoir bleu penche près du mur. Une goutte tombe de son bec. Tu joues ici un moment. La caisse d'osier est près du banc. L'herbe est froide, maman. Oui. Puis on range. On met dans la caisse. Nino touche une feuille, toute lisse. Un limaçon avance, tout lent. Après le jeu, on range. Je suis avec toi. Un oiseau crie une fois, tout loin.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6510,11 +6829,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nino va vers le jardin.
+narrateur|L'herbe est mouillée, toute brillante.
+narrateur|Ça sent la terre fraîche.
+narrateur|Un arrosoir bleu penche près du mur.
+narrateur|Une goutte tombe de son bec.
+papa|Tu joues ici un moment.
+maman|La caisse d'osier est près du banc.
+enfant-m|L'herbe est froide, maman.
+maman|Oui.
+maman|Puis on range.
+papa|On met dans la caisse.
+narrateur|Nino touche une feuille, toute lisse.
+narrateur|Un limaçon avance, tout lent.
+maman|Après le jeu, on range.
+papa|Je suis avec toi.
+narrateur|Un oiseau crie une fois, tout loin.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6539,7 +6871,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Ranger après le jeu.</t>
+          <t>L'herbe brille encore. Après le jeu, on met où ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6699,10 +7031,10 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr"/>
+          <t>narrateur|L'herbe brille encore.
+maman|Après le jeu, on met où ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6727,7 +7059,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
+          <t>Oui. On range. On met dans la caisse. Ranger, c'est mettre dans la caisse. Dans la caisse. Bravo, Nino. Tu as fait du bon travail. Nino hoche la tête. La corde de l'osier t'attend. L'arrosoir laisse une goutte.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6871,10 +7203,18 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>narrateur|Oui.
+papa|On range.
+papa|On met dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino hoche la tête.
+maman|La corde de l'osier t'attend.
+narrateur|L'arrosoir laisse une goutte.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6899,7 +7239,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu prends quel jeu ? Les cubes. Le livre. Ou la dînette.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7063,10 +7403,12 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr"/>
+          <t>papa|Tu prends quel jeu ?
+narrateur|Les cubes.
+narrateur|Le livre.
+narrateur|Ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7091,7 +7433,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
+          <t>Nino a choisi les cubes. Ils cliquent dans l'herbe mouillée. Un cube bleu a une goutte dessus. Tu fais un petit mur. Il est long. Il est solide, Nino. L'arrosoir penche encore. Après le jeu, on range. On met les cubes dans la caisse. Nino essuie un cube sur son pantalon. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7231,10 +7573,20 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nino a choisi les cubes.
+narrateur|Ils cliquent dans l'herbe mouillée.
+narrateur|Un cube bleu a une goutte dessus.
+papa|Tu fais un petit mur.
+enfant-m|Il est long.
+maman|Il est solide, Nino.
+narrateur|L'arrosoir penche encore.
+papa|Après le jeu, on range.
+maman|On met les cubes dans la caisse.
+narrateur|Nino essuie un cube sur son pantalon.
+papa|Bravo.
+papa|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7259,7 +7611,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7423,10 +7775,12 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7451,7 +7805,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. Les cubes sont un peu humides. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Une goutte brille encore sur le cube bleu.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7591,10 +7945,26 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|Les cubes sont un peu humides.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Une goutte brille encore sur le cube bleu.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7619,7 +7989,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec les cubes. C'était le matin. Après le jeu, il a mis dans la caisse. Une goutte brille encore sur le cube bleu. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7759,10 +8129,18 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Une goutte brille encore sur le cube bleu.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7787,7 +8165,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. Les cubes sont un peu humides. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. Le limaçon n'a presque plus bougé.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7927,10 +8305,26 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|Les cubes sont un peu humides.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|Le limaçon n'a presque plus bougé.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7955,7 +8349,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec les cubes. C'était après la sieste. Après le jeu, il a mis dans la caisse. Le limaçon n'a presque plus bougé. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8095,10 +8489,18 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le limaçon n'a presque plus bougé.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8123,7 +8525,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. Les cubes sont un peu humides. On range pour demain matin. C'est le soir. On range pour demain. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. Un oiseau se tait, dans le noisetier.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8263,10 +8665,26 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|Les cubes sont un peu humides.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|Un oiseau se tait, dans le noisetier.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8291,7 +8709,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec les cubes. C'était le soir. Après le jeu, il a mis dans la caisse. Un oiseau se tait, dans le noisetier. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8431,10 +8849,18 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Un oiseau se tait, dans le noisetier.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8459,7 +8885,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Nino a choisi le livre. Il l'ouvre sur le banc de pierre. Le banc est encore un peu froid. Les pages restent bien à plat. Il y a un oiseau. Oui. Un oiseau jaune. Une fourmi passe au bord du livre. Après le jeu, on range. On met le livre dans la caisse. Nino referme tout doux. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8599,10 +9025,21 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nino a choisi le livre.
+narrateur|Il l'ouvre sur le banc de pierre.
+narrateur|Le banc est encore un peu froid.
+maman|Les pages restent bien à plat.
+enfant-m|Il y a un oiseau.
+papa|Oui.
+papa|Un oiseau jaune.
+narrateur|Une fourmi passe au bord du livre.
+maman|Après le jeu, on range.
+papa|On met le livre dans la caisse.
+narrateur|Nino referme tout doux.
+maman|Bravo.
+maman|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8627,7 +9064,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8791,10 +9228,12 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8819,7 +9258,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. Le livre quitte le banc. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Une fourmi a quitté le bord du livre.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8959,10 +9398,26 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|Le livre quitte le banc.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Une fourmi a quitté le bord du livre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8987,7 +9442,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec le livre. C'était le matin. Après le jeu, il a mis dans la caisse. Une fourmi a quitté le bord du livre. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9127,10 +9582,18 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Une fourmi a quitté le bord du livre.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9155,7 +9618,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. Le livre quitte le banc. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. Le banc de pierre a gardé le chaud.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9295,10 +9758,26 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|Le livre quitte le banc.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|Le banc de pierre a gardé le chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9323,7 +9802,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec le livre. C'était après la sieste. Après le jeu, il a mis dans la caisse. Le banc de pierre a gardé le chaud. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9463,10 +9942,18 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le banc de pierre a gardé le chaud.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9491,7 +9978,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. Le livre quitte le banc. On range pour demain matin. C'est le soir. On range pour demain. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. Le vent tourne une dernière page, dehors.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9631,10 +10118,26 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|Le livre quitte le banc.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|Le vent tourne une dernière page, dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9659,7 +10162,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec le livre. C'était le soir. Après le jeu, il a mis dans la caisse. Le vent tourne une dernière page, dehors. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9799,10 +10302,18 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le vent tourne une dernière page, dehors.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9827,7 +10338,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>Nino a choisi la dînette. L'assiette pose dans l'herbe. Toc. Une goutte de l'arrosoir y tombe. C'est de la soupe d'herbe ? Oui. C'est froid. D'accord. Puis on range. La tasse penche un peu. Après le jeu, on met dans la caisse. La dînette va dans la caisse. Nino ramasse la cuillère. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9967,10 +10478,23 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Nino a choisi la dînette.
+narrateur|L'assiette pose dans l'herbe.
+narrateur|Toc.
+narrateur|Une goutte de l'arrosoir y tombe.
+maman|C'est de la soupe d'herbe ?
+enfant-m|Oui.
+enfant-m|C'est froid.
+papa|D'accord.
+papa|Puis on range.
+narrateur|La tasse penche un peu.
+maman|Après le jeu, on met dans la caisse.
+papa|La dînette va dans la caisse.
+narrateur|Nino ramasse la cuillère.
+maman|Bravo.
+maman|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9995,7 +10519,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10159,10 +10683,12 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10187,7 +10713,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. L'assiette quitte l'herbe. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. L'herbe a laissé une trace sur l'assiette.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10327,10 +10853,26 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|L'assiette quitte l'herbe.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|L'herbe a laissé une trace sur l'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10355,7 +10897,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec la dînette. C'était le matin. Après le jeu, il a mis dans la caisse. L'herbe a laissé une trace sur l'assiette. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10495,10 +11037,18 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|L'herbe a laissé une trace sur l'assiette.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10523,7 +11073,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. L'assiette quitte l'herbe. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. La tasse est un peu tiède encore.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10663,10 +11213,26 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|L'assiette quitte l'herbe.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|La tasse est un peu tiède encore.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10691,7 +11257,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec la dînette. C'était après la sieste. Après le jeu, il a mis dans la caisse. La tasse est un peu tiède encore. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10831,10 +11397,18 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|La tasse est un peu tiède encore.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10859,7 +11433,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans le jardin. L'assiette quitte l'herbe. On range pour demain matin. C'est le soir. On range pour demain. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. Un grillon chante, tout près du mur.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10999,10 +11573,26 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans le jardin.
+narrateur|L'assiette quitte l'herbe.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|Un grillon chante, tout près du mur.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11027,7 +11617,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par le jardin. Il a joué avec la dînette. C'était le soir. Après le jeu, il a mis dans la caisse. Un grillon chante, tout près du mur. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11167,10 +11757,18 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Un grillon chante, tout près du mur.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11195,7 +11793,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Nino va vers la chambre. Le parquet craque, tout doux. La couverture de laine est encore chaude. Un rideau jaune bouge un peu. La veilleuse fait un rond orange. Tu joues ici un moment. La caisse d'osier est près du lit. C'est calme, ici. Oui. Puis on range. On met dans la caisse. Nino pose la main sur l'oreiller. L'oreiller sent le savon. Après le jeu, on range. Je suis avec toi. Le rideau laisse un filet de jour.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11335,11 +11933,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nino va vers la chambre.
+narrateur|Le parquet craque, tout doux.
+narrateur|La couverture de laine est encore chaude.
+narrateur|Un rideau jaune bouge un peu.
+narrateur|La veilleuse fait un rond orange.
+maman|Tu joues ici un moment.
+papa|La caisse d'osier est près du lit.
+enfant-m|C'est calme, ici.
+papa|Oui.
+papa|Puis on range.
+maman|On met dans la caisse.
+narrateur|Nino pose la main sur l'oreiller.
+narrateur|L'oreiller sent le savon.
+papa|Après le jeu, on range.
+maman|Je suis avec toi.
+narrateur|Le rideau laisse un filet de jour.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11364,7 +11975,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Ranger après le jeu.</t>
+          <t>Le rideau bouge encore. Après le jeu, on met où ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11524,10 +12135,10 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr"/>
+          <t>narrateur|Le rideau bouge encore.
+maman|Après le jeu, on met où ?</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11552,7 +12163,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
+          <t>Oui. On range. On met dans la caisse. Ranger, c'est mettre dans la caisse. Dans la caisse. Bravo, Nino. Tu as fait du bon travail. Nino hoche la tête. La corde de l'osier t'attend. La veilleuse reste allumée.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11696,10 +12307,18 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Tom respire. Tom retient : ranger, caisse. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr"/>
+          <t>narrateur|Oui.
+papa|On range.
+papa|On met dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino hoche la tête.
+maman|La corde de l'osier t'attend.
+narrateur|La veilleuse reste allumée.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11724,7 +12343,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu prends quel jeu ? Les cubes. Le livre. Ou la dînette.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11888,10 +12507,12 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr"/>
+          <t>papa|Tu prends quel jeu ?
+narrateur|Les cubes.
+narrateur|Le livre.
+narrateur|Ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11916,7 +12537,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
+          <t>Nino a choisi les cubes. Ils cliquent sur le parquet. Un cube rouge roule sous le rideau. Tu fais une maison. Elle a une porte. Elle est jolie, Nino. La veilleuse éclaire un cube. Après le jeu, on range. On met les cubes dans la caisse. Nino rattrape le cube rouge. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12056,10 +12677,20 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nino a choisi les cubes.
+narrateur|Ils cliquent sur le parquet.
+narrateur|Un cube rouge roule sous le rideau.
+papa|Tu fais une maison.
+enfant-m|Elle a une porte.
+maman|Elle est jolie, Nino.
+narrateur|La veilleuse éclaire un cube.
+papa|Après le jeu, on range.
+maman|On met les cubes dans la caisse.
+narrateur|Nino rattrape le cube rouge.
+papa|Bravo.
+papa|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12084,7 +12715,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12248,10 +12879,12 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12276,7 +12909,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. Les cubes quittent le parquet. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Le cube rouge a quitté le rideau.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12416,10 +13049,26 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|Les cubes quittent le parquet.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Le cube rouge a quitté le rideau.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12444,7 +13093,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec les cubes. C'était le matin. Après le jeu, il a mis dans la caisse. Le cube rouge a quitté le rideau. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12584,10 +13233,18 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le cube rouge a quitté le rideau.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12612,7 +13269,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. Les cubes quittent le parquet. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. L'oreiller a gardé un creux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12752,10 +13409,26 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|Les cubes quittent le parquet.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|L'oreiller a gardé un creux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12780,7 +13453,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec les cubes. C'était après la sieste. Après le jeu, il a mis dans la caisse. L'oreiller a gardé un creux. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12920,10 +13593,18 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|L'oreiller a gardé un creux.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12948,7 +13629,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. Les cubes quittent le parquet. On range pour demain matin. C'est le soir. On range pour demain. Nino met les cubes dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. La veilleuse fait encore son rond.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13088,10 +13769,26 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|Les cubes quittent le parquet.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met les cubes dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|La veilleuse fait encore son rond.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13116,7 +13813,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec les cubes. C'était le soir. Après le jeu, il a mis dans la caisse. La veilleuse fait encore son rond. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13256,10 +13953,18 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|La veilleuse fait encore son rond.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13284,7 +13989,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Nino a choisi le livre. Il l'ouvre sur l'oreiller. L'oreiller est encore tiède. Tu tournes les pages, tout lent. Il y a une lune. Oui. Une lune ronde. Le rideau fait une ombre sur la page. Après le jeu, on range. On met le livre dans la caisse. Nino ferme le livre. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13424,10 +14129,21 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nino a choisi le livre.
+narrateur|Il l'ouvre sur l'oreiller.
+narrateur|L'oreiller est encore tiède.
+maman|Tu tournes les pages, tout lent.
+enfant-m|Il y a une lune.
+papa|Oui.
+papa|Une lune ronde.
+narrateur|Le rideau fait une ombre sur la page.
+maman|Après le jeu, on range.
+papa|On met le livre dans la caisse.
+narrateur|Nino ferme le livre.
+maman|Bravo.
+maman|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13452,7 +14168,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13616,10 +14332,12 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13644,7 +14362,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. Le livre quitte l'oreiller. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Le filet de jour touche le livre fermé.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13784,10 +14502,26 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|Le livre quitte l'oreiller.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Le filet de jour touche le livre fermé.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13812,7 +14546,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec le livre. C'était le matin. Après le jeu, il a mis dans la caisse. Le filet de jour touche le livre fermé. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13952,10 +14686,18 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le filet de jour touche le livre fermé.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13980,7 +14722,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. Le livre quitte l'oreiller. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. La page a tiédi contre la joue.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14120,10 +14862,26 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|Le livre quitte l'oreiller.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|La page a tiédi contre la joue.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14148,7 +14906,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec le livre. C'était après la sieste. Après le jeu, il a mis dans la caisse. La page a tiédi contre la joue. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14288,10 +15046,18 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|La page a tiédi contre la joue.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14316,7 +15082,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. Le livre quitte l'oreiller. On range pour demain matin. C'est le soir. On range pour demain. Nino met le livre dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. La lune du livre dort dans la caisse.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14456,10 +15222,26 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|Le livre quitte l'oreiller.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met le livre dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|La lune du livre dort dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14484,7 +15266,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec le livre. C'était le soir. Après le jeu, il a mis dans la caisse. La lune du livre dort dans la caisse. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14624,10 +15406,18 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|La lune du livre dort dans la caisse.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14652,7 +15442,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>Nino a choisi la dînette. La tasse tape près du lit. Toc. Ça sent encore le savon de l'oreiller. Tu sers le thé ? Oui. C'est chaud. D'accord. Puis on range. L'assiette glisse un peu sur le plaid. Après le jeu, on met dans la caisse. La dînette va dans la caisse. Nino pose la cuillère. Bravo. La caisse t'attend.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14792,10 +15582,23 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Tom répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Nino a choisi la dînette.
+narrateur|La tasse tape près du lit.
+narrateur|Toc.
+narrateur|Ça sent encore le savon de l'oreiller.
+maman|Tu sers le thé ?
+enfant-m|Oui.
+enfant-m|C'est chaud.
+papa|D'accord.
+papa|Puis on range.
+narrateur|L'assiette glisse un peu sur le plaid.
+maman|Après le jeu, on met dans la caisse.
+papa|La dînette va dans la caisse.
+narrateur|Nino pose la cuillère.
+maman|Bravo.
+maman|La caisse t'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14820,7 +15623,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour ranger ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14984,10 +15787,12 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr"/>
+          <t>maman|C'est quel moment, pour ranger ?
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15012,7 +15817,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. La dînette quitte le plaid. C'est l'heure de ranger. C'est le matin. On range, puis le chemin de l'école. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Ils prennent le cartable. Les chaussures font toc toc, près du banc. On y va. Tu as fait du bon travail. Un chausson reste près de la tasse.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15152,10 +15957,26 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|La dînette quitte le plaid.
+maman|C'est l'heure de ranger.
+papa|C'est le matin.
+papa|On range, puis le chemin de l'école.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Ils prennent le cartable.
+narrateur|Les chaussures font toc toc, près du banc.
+maman|On y va.
+maman|Tu as fait du bon travail.
+narrateur|Un chausson reste près de la tasse.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15180,7 +16001,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec la dînette. C'était le matin. Après le jeu, il a mis dans la caisse. Un chausson reste près de la tasse. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15320,10 +16141,18 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Un chausson reste près de la tasse.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15348,7 +16177,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. La dînette quitte le plaid. Après la sieste, on range. C'est après la sieste. Plus tard, le chemin. D'abord la caisse. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Nino bâille un tout petit peu. La caisse est prête. Tu as fait du bon travail. Le plaid a un pli en forme d'assiette.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15488,10 +16317,26 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|La dînette quitte le plaid.
+maman|Après la sieste, on range.
+maman|C'est après la sieste.
+papa|Plus tard, le chemin.
+papa|D'abord la caisse.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nino bâille un tout petit peu.
+papa|La caisse est prête.
+maman|Tu as fait du bon travail.
+narrateur|Le plaid a un pli en forme d'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15516,7 +16361,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec la dînette. C'était après la sieste. Après le jeu, il a mis dans la caisse. Le plaid a un pli en forme d'assiette. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15656,10 +16501,18 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|Le plaid a un pli en forme d'assiette.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15684,7 +16537,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
+          <t>Nino a fini de jouer dans la chambre. La dînette quitte le plaid. On range pour demain matin. C'est le soir. On range pour demain. Nino met la dînette dans la caisse. Toc. L'osier répond. Bravo. J'ai rangé. Oui. Tu as mis dans la caisse. Ranger, c'est mettre dans la caisse. Le réverbère s'allume déjà, dehors. Merci, Nino. C'est du bon travail. On laisse la caisse près du banc. La chambre est calme, tout à fait.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15824,10 +16677,26 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Tom a entendu : ranger, caisse. Tom dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Nino a fini de jouer dans la chambre.
+narrateur|La dînette quitte le plaid.
+maman|On range pour demain matin.
+papa|C'est le soir.
+papa|On range pour demain.
+narrateur|Nino met la dînette dans la caisse.
+narrateur|Toc.
+narrateur|L'osier répond.
+maman|Bravo.
+enfant-m|J'ai rangé.
+papa|Oui.
+papa|Tu as mis dans la caisse.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Le réverbère s'allume déjà, dehors.
+maman|Merci, Nino.
+maman|C'est du bon travail.
+papa|On laisse la caisse près du banc.
+narrateur|La chambre est calme, tout à fait.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15852,7 +16721,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une feuille jaune colle encore au bonnet. Nino est passé par la chambre. Il a joué avec la dînette. C'était le soir. Après le jeu, il a mis dans la caisse. La chambre est calme, tout à fait. Tu as rangé. Bravo. La caisse d'osier est près du banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15992,10 +16861,18 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr"/>
+          <t>narrateur|Une feuille jaune colle encore au bonnet.
+narrateur|Nino est passé par la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|Après le jeu, il a mis dans la caisse.
+narrateur|La chambre est calme, tout à fait.
+maman|Tu as rangé.
+maman|Bravo.
+papa|La caisse d'osier est près du banc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16014,7 +16891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16052,6 +16929,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-039.xlsx
+++ b/stories/arbres/TREE-AUT-039.xlsx
@@ -2939,17 +2939,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Le lièvre a le nez contre la poche. Nino porte la caisse, la corde à la paume. C'est moi le porteur, papa. Oui, elle est légère, maintenant. Le cube jaune garde un peu d'orange. Ils ont cherché dans la cuisine. La casserole tic, derrière eux. La rosée sèche sur le banc de mousse. Le chemin reprend, bas et clair.</t>
+          <t>Le lièvre a le nez contre la poche. Nino porte la caisse, la corde à la paume. C'est moi le porteur, papa. Oui, elle est légère, maintenant. Le cube jaune garde un peu d'orange. Ils ont cherché dans la cuisine. La casserole tic, derrière eux. La rosée sèche sur le banc de mousse. Nino avance, la caisse contre la hanche.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le lièvre a le nez contre la poche. Nino porte la caisse, la corde à la paume. C'est moi le porteur, papa. Oui, elle est légère, maintenant. Le cube jaune garde un peu d'orange. Ils ont cherché dans la cuisine. La casserole tic, derrière eux. La rosée sèche sur le banc de mousse. Le chemin reprend, bas et clair.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le lièvre a le nez contre la poche. Nino porte la caisse, la corde à la paume. C'est moi le porteur, papa. Oui, elle est légère, maintenant. Le cube jaune garde un peu d'orange. Ils ont cherché dans la cuisine. La casserole tic, derrière eux. La rosée sèche sur le banc de mousse. Nino avance, la caisse contre la hanche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le lièvre a le nez contre la poche. Nino porte la caisse, la corde à la paume. C'est moi le porteur, papa. Oui, elle est légère, maintenant. Le cube jaune garde un peu d'orange. Ils ont cherché dans la cuisine. La casserole tic, derrière eux. La rosée sèche sur le banc de mousse. Le chemin reprend, bas et clair.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le lièvre a le nez contre la poche. Nino porte la caisse, la corde à la paume. C'est moi le porteur, papa. Oui, elle est légère, maintenant. Le cube jaune garde un peu d'orange. Ils ont cherché dans la cuisine. La casserole tic, derrière eux. La rosée sèche sur le banc de mousse. Nino avance, la caisse contre la hanche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3091,7 +3091,7 @@
 narrateur|Ils ont cherché dans la cuisine.
 narrateur|La casserole tic, derrière eux.
 narrateur|La rosée sèche sur le banc de mousse.
-narrateur|Le chemin reprend, bas et clair.</t>
+narrateur|Nino avance, la caisse contre la hanche.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3681,17 +3681,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Contre la joue, le lièvre est calme. Nino pose la caisse près de la grille. Les cubes font des ombres, dehors. La rue les a prises. Merci d'avoir porté jusqu'ici. L'ombre des cubes danse sous la lampe. La grille de cave est noire. Dehors, les lumières des maisons s'allument. L'osier ne cache plus rien.</t>
+          <t>Contre la joue, le lièvre est calme. Nino pose la caisse près de la grille. Les cubes font des ombres, dehors. La rue les a prises. Merci d'avoir porté jusqu'ici. L'ombre des cubes danse sous la lampe. La grille de cave est noire. Dehors, les lumières des maisons s'allument. La corde reste dans sa paume, sûre.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Contre la joue, le lièvre est calme. Nino pose la caisse près de la grille. Les cubes font des ombres, dehors. La rue les a prises. Merci d'avoir porté jusqu'ici. L'ombre des cubes danse sous la lampe. La grille de cave est noire. Dehors, les lumières des maisons s'allument. L'osier ne cache plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Contre la joue, le lièvre est calme. Nino pose la caisse près de la grille. Les cubes font des ombres, dehors. La rue les a prises. Merci d'avoir porté jusqu'ici. L'ombre des cubes danse sous la lampe. La grille de cave est noire. Dehors, les lumières des maisons s'allument. La corde reste dans sa paume, sûre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Contre la joue, le lièvre est calme. Nino pose la caisse près de la grille. Les cubes font des ombres, dehors. La rue les a prises. Merci d'avoir porté jusqu'ici. L'ombre des cubes danse sous la lampe. La grille de cave est noire. Dehors, les lumières des maisons s'allument. L'osier ne cache plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Contre la joue, le lièvre est calme. Nino pose la caisse près de la grille. Les cubes font des ombres, dehors. La rue les a prises. Merci d'avoir porté jusqu'ici. L'ombre des cubes danse sous la lampe. La grille de cave est noire. Dehors, les lumières des maisons s'allument. La corde reste dans sa paume, sûre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3833,7 +3833,7 @@
 narrateur|L'ombre des cubes danse sous la lampe.
 narrateur|La grille de cave est noire.
 narrateur|Dehors, les lumières des maisons s'allument.
-narrateur|L'osier ne cache plus rien.</t>
+narrateur|La corde reste dans sa paume, sûre.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -6316,17 +6316,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Voilà le lièvre, contre le cartable. Nino pose la caisse sur le banc tiède. Il avait sa place à table. Au fond, oui. La cuillère a fini de briller. Une cuillère minuscule brille moins. Les joues de Nino sont chaudes. L'osier sent l'orange, un peu. Le banc garde leur poids.</t>
+          <t>Voilà le lièvre, contre le cartable. Nino pose la caisse sur le banc tiède. Il avait sa place à table. Au fond, oui. La cuillère a fini de briller. Une cuillère minuscule brille moins. Les joues de Nino sont chaudes. L'osier sent l'orange, un peu. La tasse miniature s'est tue, au fond.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Voilà le lièvre, contre le cartable. Nino pose la caisse sur le banc tiède. Il avait sa place à table. Au fond, oui. La cuillère a fini de briller. Une cuillère minuscule brille moins. Les joues de Nino sont chaudes. L'osier sent l'orange, un peu. Le banc garde leur poids.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Voilà le lièvre, contre le cartable. Nino pose la caisse sur le banc tiède. Il avait sa place à table. Au fond, oui. La cuillère a fini de briller. Une cuillère minuscule brille moins. Les joues de Nino sont chaudes. L'osier sent l'orange, un peu. La tasse miniature s'est tue, au fond.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Voilà le lièvre, contre le cartable. Nino pose la caisse sur le banc tiède. Il avait sa place à table. Au fond, oui. La cuillère a fini de briller. Une cuillère minuscule brille moins. Les joues de Nino sont chaudes. L'osier sent l'orange, un peu. Le banc garde leur poids.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Voilà le lièvre, contre le cartable. Nino pose la caisse sur le banc tiède. Il avait sa place à table. Au fond, oui. La cuillère a fini de briller. Une cuillère minuscule brille moins. Les joues de Nino sont chaudes. L'osier sent l'orange, un peu. La tasse miniature s'est tue, au fond.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
 narrateur|Une cuillère minuscule brille moins.
 narrateur|Les joues de Nino sont chaudes.
 narrateur|L'osier sent l'orange, un peu.
-narrateur|Le banc garde leur poids.</t>
+narrateur|La tasse miniature s'est tue, au fond.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -9704,17 +9704,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Une goutte d'herbe sèche sur l'oreille. Nino porte la caisse, le livre au fond. La page est fraîche. Le chemin aussi. Le cartable te rejoint. Le livre a une page un peu fraîche. La rosée sèche sur le banc de mousse. Le moineau s'est envolé. Les pas reprennent, clairs.</t>
+          <t>Une goutte d'herbe sèche sur l'oreille. Nino porte la caisse, le livre au fond. La page est fraîche. Le chemin aussi. Le cartable te rejoint. Le livre a une page un peu fraîche. La rosée sèche sur le banc de mousse. Le moineau s'est envolé. Le livre frais tape le fond, au rythme des pas.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une goutte d'herbe sèche sur l'oreille. Nino porte la caisse, le livre au fond. La page est fraîche. Le chemin aussi. Le cartable te rejoint. Le livre a une page un peu fraîche. La rosée sèche sur le banc de mousse. Le moineau s'est envolé. Les pas reprennent, clairs.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une goutte d'herbe sèche sur l'oreille. Nino porte la caisse, le livre au fond. La page est fraîche. Le chemin aussi. Le cartable te rejoint. Le livre a une page un peu fraîche. La rosée sèche sur le banc de mousse. Le moineau s'est envolé. Le livre frais tape le fond, au rythme des pas.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une goutte d'herbe sèche sur l'oreille. Nino porte la caisse, le livre au fond. La page est fraîche. Le chemin aussi. Le cartable te rejoint. Le livre a une page un peu fraîche. La rosée sèche sur le banc de mousse. Le moineau s'est envolé. Les pas reprennent, clairs.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une goutte d'herbe sèche sur l'oreille. Nino porte la caisse, le livre au fond. La page est fraîche. Le chemin aussi. Le cartable te rejoint. Le livre a une page un peu fraîche. La rosée sèche sur le banc de mousse. Le moineau s'est envolé. Le livre frais tape le fond, au rythme des pas.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9856,7 +9856,7 @@
 narrateur|Le livre a une page un peu fraîche.
 narrateur|La rosée sèche sur le banc de mousse.
 narrateur|Le moineau s'est envolé.
-narrateur|Les pas reprennent, clairs.</t>
+narrateur|Le livre frais tape le fond, au rythme des pas.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -11578,17 +11578,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Dans la paume, le bois est un peu frais. Nino pose la caisse sur le banc tiède. Son thé a attendu. Toi aussi. La cuillère est moins froide. L'osier sent le jardin tiède. Les joues de Nino restent chaudes. Une feuille reste dans l'assiette. Le banc garde leur poids.</t>
+          <t>Dans la paume, le bois est un peu frais. Nino pose la caisse sur le banc tiède. Son thé a attendu. Toi aussi. La cuillère est moins froide. L'osier sent le jardin tiède. Les joues de Nino restent chaudes. Une feuille reste dans l'assiette. L'herbe lâche leurs chaussures, enfin.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Dans la paume, le bois est un peu frais. Nino pose la caisse sur le banc tiède. Son thé a attendu. Toi aussi. La cuillère est moins froide. L'osier sent le jardin tiède. Les joues de Nino restent chaudes. Une feuille reste dans l'assiette. Le banc garde leur poids.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Dans la paume, le bois est un peu frais. Nino pose la caisse sur le banc tiède. Son thé a attendu. Toi aussi. La cuillère est moins froide. L'osier sent le jardin tiède. Les joues de Nino restent chaudes. Une feuille reste dans l'assiette. L'herbe lâche leurs chaussures, enfin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Dans la paume, le bois est un peu frais. Nino pose la caisse sur le banc tiède. Son thé a attendu. Toi aussi. La cuillère est moins froide. L'osier sent le jardin tiède. Les joues de Nino restent chaudes. Une feuille reste dans l'assiette. Le banc garde leur poids.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Dans la paume, le bois est un peu frais. Nino pose la caisse sur le banc tiède. Son thé a attendu. Toi aussi. La cuillère est moins froide. L'osier sent le jardin tiède. Les joues de Nino restent chaudes. Une feuille reste dans l'assiette. L'herbe lâche leurs chaussures, enfin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11730,7 +11730,7 @@
 narrateur|L'osier sent le jardin tiède.
 narrateur|Les joues de Nino restent chaudes.
 narrateur|Une feuille reste dans l'assiette.
-narrateur|Le banc garde leur poids.</t>
+narrateur|L'herbe lâche leurs chaussures, enfin.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Nino souffle sur l'oreille du lièvre. L'assiette garde un rond de lampe. C'est son soleil. La rue en a un, trop. Passe, je ferme le pas. La petite assiette reflète le réverbère. La grille de cave est noire. Les maisons s'allument. Nino pose la caisse derrière la porte.</t>
+          <t>Nino souffle sur l'oreille du lièvre. L'assiette garde un rond de lampe. C'est son soleil. La rue a le sien, jaune. Passe, je ferme le pas. La petite assiette reflète le réverbère. La grille de cave est noire. Les maisons s'allument. Nino pose la caisse derrière la porte.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino souffle sur l'oreille du lièvre. L'assiette garde un rond de lampe. C'est son soleil. La rue en a un, trop. Passe, je ferme le pas. La petite assiette reflète le réverbère. La grille de cave est noire. Les maisons s'allument. Nino pose la caisse derrière la porte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino souffle sur l'oreille du lièvre. L'assiette garde un rond de lampe. C'est son soleil. La rue a le sien, jaune. Passe, je ferme le pas. La petite assiette reflète le réverbère. La grille de cave est noire. Les maisons s'allument. Nino pose la caisse derrière la porte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino souffle sur l'oreille du lièvre. L'assiette garde un rond de lampe. C'est son soleil. La rue en a un, trop. Passe, je ferme le pas. La petite assiette reflète le réverbère. La grille de cave est noire. Les maisons s'allument. Nino pose la caisse derrière la porte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino souffle sur l'oreille du lièvre. L'assiette garde un rond de lampe. C'est son soleil. La rue a le sien, jaune. Passe, je ferme le pas. La petite assiette reflète le réverbère. La grille de cave est noire. Les maisons s'allument. Nino pose la caisse derrière la porte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12096,7 +12096,7 @@
           <t>narrateur|Nino souffle sur l'oreille du lièvre.
 narrateur|L'assiette garde un rond de lampe.
 enfant-m|C'est son soleil.
-papa|La rue en a un, trop.
+papa|La rue a le sien, jaune.
 maman|Passe, je ferme le pas.
 narrateur|La petite assiette reflète le réverbère.
 narrateur|La grille de cave est noire.
@@ -13277,17 +13277,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>La lumière est pâle, un peu bleue. Nino glisse les cubes, un par un. Un cube tapote le parquet. Au fond, l'oreille de bois. Le chemin l'a mené là. Le vrai chemin, c'était l'osier. Le cartable est contre la chaise. Nino met le lièvre dans la poche. Il porte la caisse vers la porte. Le bonnet rejoint sa tête. La rosée sèche sur le banc. Le rideau jaune ne le retient plus.</t>
+          <t>La lumière est pâle, un peu bleue. Nino glisse les cubes, un par un. Un cube tapote le parquet. Au fond, l'oreille de bois. Le chemin l'a mené là. Il était au fond, Nino. Le cartable est contre la chaise. Nino met le lièvre dans la poche. Il porte la caisse vers la porte. Le bonnet rejoint sa tête. La rosée sèche sur le banc. Le rideau jaune ne le retient plus.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La lumière est pâle, un peu bleue. Nino glisse les cubes, un par un. Un cube tapote le parquet. Au fond, l'oreille de bois. Le chemin l'a mené là. Le vrai chemin, c'était l'osier. Le cartable est contre la chaise. Nino met le &lt;emphasis level="moderate"&gt;lièvre&lt;/emphasis&gt; dans la poche. Il porte la caisse vers la porte. Le bonnet rejoint sa tête. La rosée sèche sur le banc. Le rideau jaune ne le retient plus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La lumière est pâle, un peu bleue. Nino glisse les cubes, un par un. Un cube tapote le parquet. Au fond, l'oreille de bois. Le chemin l'a mené là. Il était au fond, Nino. Le cartable est contre la chaise. Nino met le &lt;emphasis level="moderate"&gt;lièvre&lt;/emphasis&gt; dans la poche. Il porte la caisse vers la porte. Le bonnet rejoint sa tête. La rosée sèche sur le banc. Le rideau jaune ne le retient plus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>La lumière est pâle, un peu bleue. Nino glisse les cubes, un par un. Un cube tapote le parquet. Au fond, l'oreille de bois. Le chemin l'a mené là. Le vrai chemin, c'était l'osier. Le cartable est contre la chaise. Nino met le &lt;emphasis&gt;lièvre&lt;/emphasis&gt; dans la poche. Il porte la caisse vers la porte. Le bonnet rejoint sa tête. La rosée sèche sur le banc. Le rideau jaune ne le retient plus. [pause]</t>
+          <t>La lumière est pâle, un peu bleue. Nino glisse les cubes, un par un. Un cube tapote le parquet. Au fond, l'oreille de bois. Le chemin l'a mené là. Il était au fond, Nino. Le cartable est contre la chaise. Nino met le &lt;emphasis&gt;lièvre&lt;/emphasis&gt; dans la poche. Il porte la caisse vers la porte. Le bonnet rejoint sa tête. La rosée sèche sur le banc. Le rideau jaune ne le retient plus. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13426,7 +13426,7 @@
 narrateur|Un cube tapote le parquet.
 narrateur|Au fond, l'oreille de bois.
 enfant-m|Le chemin l'a mené là.
-maman|Le vrai chemin, c'était l'osier.
+maman|Il était au fond, Nino.
 papa|Le cartable est contre la chaise.
 narrateur|Nino met le lièvre dans la poche.
 narrateur|Il porte la caisse vers la porte.
@@ -13464,17 +13464,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Le cartable attend, sage, à côté. Nino porte la caisse, les cubes au fond. Le chemin de cubes est fini. Le vrai chemin est dehors. Le bonnet est sur ta tête. Un cube tapote le fond, très bas. La rosée sèche sur le banc de mousse. Le rideau jaune reste derrière. Les pas reprennent, clairs.</t>
+          <t>Le cartable attend, sage, à côté. Nino porte la caisse, les cubes au fond. Le chemin de cubes est fini. Dehors, le banc t'attend. Le bonnet est sur ta tête. Un cube tapote le fond, très bas. La rosée sèche sur le banc de mousse. Le rideau jaune reste derrière. Un cube tapote au rythme des pas.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable attend, sage, à côté. Nino porte la caisse, les cubes au fond. Le chemin de cubes est fini. Le vrai chemin est dehors. Le bonnet est sur ta tête. Un cube tapote le fond, très bas. La rosée sèche sur le banc de mousse. Le rideau jaune reste derrière. Les pas reprennent, clairs.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable attend, sage, à côté. Nino porte la caisse, les cubes au fond. Le chemin de cubes est fini. Dehors, le banc t'attend. Le bonnet est sur ta tête. Un cube tapote le fond, très bas. La rosée sèche sur le banc de mousse. Le rideau jaune reste derrière. Un cube tapote au rythme des pas.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable attend, sage, à côté. Nino porte la caisse, les cubes au fond. Le chemin de cubes est fini. Le vrai chemin est dehors. Le bonnet est sur ta tête. Un cube tapote le fond, très bas. La rosée sèche sur le banc de mousse. Le rideau jaune reste derrière. Les pas reprennent, clairs.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable attend, sage, à côté. Nino porte la caisse, les cubes au fond. Le chemin de cubes est fini. Dehors, le banc t'attend. Le bonnet est sur ta tête. Un cube tapote le fond, très bas. La rosée sèche sur le banc de mousse. Le rideau jaune reste derrière. Un cube tapote au rythme des pas.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13611,12 +13611,12 @@
           <t>narrateur|Le cartable attend, sage, à côté.
 narrateur|Nino porte la caisse, les cubes au fond.
 enfant-m|Le chemin de cubes est fini.
-papa|Le vrai chemin est dehors.
+papa|Dehors, le banc t'attend.
 maman|Le bonnet est sur ta tête.
 narrateur|Un cube tapote le fond, très bas.
 narrateur|La rosée sèche sur le banc de mousse.
 narrateur|Le rideau jaune reste derrière.
-narrateur|Les pas reprennent, clairs.</t>
+narrateur|Un cube tapote au rythme des pas.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -14206,17 +14206,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Le lièvre a un grain de lumière. Nino porte la caisse dans le couloir. Les cubes dansaient sur le mur. La veilleuse les a pris. La rue s'allume, elle aussi. L'ombre des cubes danse sur le mur. Les maisons, dehors, s'allument. La chambre garde un carré de veilleuse. L'osier ne cache plus rien.</t>
+          <t>Le lièvre a un grain de lumière. Nino porte la caisse dans le couloir. Les cubes dansaient sur le mur. La veilleuse les a pris. La rue s'allume, elle aussi. L'ombre des cubes danse sur le mur. Les maisons, dehors, s'allument. La chambre garde un carré de veilleuse. Le couloir sent le foin, un instant.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le lièvre a un grain de lumière. Nino porte la caisse dans le couloir. Les cubes dansaient sur le mur. La veilleuse les a pris. La rue s'allume, elle aussi. L'ombre des cubes danse sur le mur. Les maisons, dehors, s'allument. La chambre garde un carré de veilleuse. L'osier ne cache plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le lièvre a un grain de lumière. Nino porte la caisse dans le couloir. Les cubes dansaient sur le mur. La veilleuse les a pris. La rue s'allume, elle aussi. L'ombre des cubes danse sur le mur. Les maisons, dehors, s'allument. La chambre garde un carré de veilleuse. Le couloir sent le foin, un instant.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le lièvre a un grain de lumière. Nino porte la caisse dans le couloir. Les cubes dansaient sur le mur. La veilleuse les a pris. La rue s'allume, elle aussi. L'ombre des cubes danse sur le mur. Les maisons, dehors, s'allument. La chambre garde un carré de veilleuse. L'osier ne cache plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le lièvre a un grain de lumière. Nino porte la caisse dans le couloir. Les cubes dansaient sur le mur. La veilleuse les a pris. La rue s'allume, elle aussi. L'ombre des cubes danse sur le mur. Les maisons, dehors, s'allument. La chambre garde un carré de veilleuse. Le couloir sent le foin, un instant.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14358,7 +14358,7 @@
 narrateur|L'ombre des cubes danse sur le mur.
 narrateur|Les maisons, dehors, s'allument.
 narrateur|La chambre garde un carré de veilleuse.
-narrateur|L'osier ne cache plus rien.</t>
+narrateur|Le couloir sent le foin, un instant.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -14967,17 +14967,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Nino referme la main autour du bois. Il porte la caisse, le livre au fond. Le rideau a laissé du jaune. Sur la page, oui. Le banc t'attend. Une bande jaune colore la page. La rosée sèche sur le banc de pierre. Le cartable fait zzz. Le chemin reprend, bas et clair.</t>
+          <t>Nino referme la main autour du bois. Il porte la caisse, le livre au fond. Le rideau a laissé du jaune. Sur la page, oui. Le banc t'attend. Une bande jaune colore la page. La rosée sèche sur le banc de pierre. Le cartable fait zzz. La bande jaune voyage avec la page.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino referme la main autour du bois. Il porte la caisse, le livre au fond. Le rideau a laissé du jaune. Sur la page, oui. Le banc t'attend. Une bande jaune colore la page. La rosée sèche sur le banc de pierre. Le cartable fait zzz. Le chemin reprend, bas et clair.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino referme la main autour du bois. Il porte la caisse, le livre au fond. Le rideau a laissé du jaune. Sur la page, oui. Le banc t'attend. Une bande jaune colore la page. La rosée sèche sur le banc de pierre. Le cartable fait zzz. La bande jaune voyage avec la page.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino referme la main autour du bois. Il porte la caisse, le livre au fond. Le rideau a laissé du jaune. Sur la page, oui. Le banc t'attend. Une bande jaune colore la page. La rosée sèche sur le banc de pierre. Le cartable fait zzz. Le chemin reprend, bas et clair.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino referme la main autour du bois. Il porte la caisse, le livre au fond. Le rideau a laissé du jaune. Sur la page, oui. Le banc t'attend. Une bande jaune colore la page. La rosée sèche sur le banc de pierre. Le cartable fait zzz. La bande jaune voyage avec la page.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15119,7 +15119,7 @@
 narrateur|Une bande jaune colore la page.
 narrateur|La rosée sèche sur le banc de pierre.
 narrateur|Le cartable fait zzz.
-narrateur|Le chemin reprend, bas et clair.</t>
+narrateur|La bande jaune voyage avec la page.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -16470,17 +16470,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Nino a le bois contre le cœur. Il porte la caisse, la tasse au fond. Le thé de chambre est fini. Le chemin, lui, commence. Le cartable fait zzz. Une tasse miniature est au fond. La rosée sèche sur le banc de mousse. La fermeture du cartable se tait. Les pas reprennent, clairs.</t>
+          <t>Nino a le bois contre le cœur. Il porte la caisse, la tasse au fond. Le thé de chambre est fini. Le chemin, lui, commence. Le cartable fait zzz. Une tasse miniature est au fond. La rosée sèche sur le banc de mousse. Zzz, le cartable se tait. Sans ting, la tasse voyage au fond.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a le bois contre le cœur. Il porte la caisse, la tasse au fond. Le thé de chambre est fini. Le chemin, lui, commence. Le cartable fait zzz. Une tasse miniature est au fond. La rosée sèche sur le banc de mousse. La fermeture du cartable se tait. Les pas reprennent, clairs.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a le bois contre le cœur. Il porte la caisse, la tasse au fond. Le thé de chambre est fini. Le chemin, lui, commence. Le cartable fait zzz. Une tasse miniature est au fond. La rosée sèche sur le banc de mousse. Zzz, le cartable se tait. Sans ting, la tasse voyage au fond.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a le bois contre le cœur. Il porte la caisse, la tasse au fond. Le thé de chambre est fini. Le chemin, lui, commence. Le cartable fait zzz. Une tasse miniature est au fond. La rosée sèche sur le banc de mousse. La fermeture du cartable se tait. Les pas reprennent, clairs.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a le bois contre le cœur. Il porte la caisse, la tasse au fond. Le thé de chambre est fini. Le chemin, lui, commence. Le cartable fait zzz. Une tasse miniature est au fond. La rosée sèche sur le banc de mousse. Zzz, le cartable se tait. Sans ting, la tasse voyage au fond.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16621,8 +16621,8 @@
 papa|Le cartable fait zzz.
 narrateur|Une tasse miniature est au fond.
 narrateur|La rosée sèche sur le banc de mousse.
-narrateur|La fermeture du cartable se tait.
-narrateur|Les pas reprennent, clairs.</t>
+narrateur|Zzz, le cartable se tait.
+narrateur|Sans ting, la tasse voyage au fond.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -17390,7 +17390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17447,6 +17447,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
